--- a/templates/ci_us/CI_template_footer_US.xlsx
+++ b/templates/ci_us/CI_template_footer_US.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,13 +78,6 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -579,148 +572,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -807,29 +800,36 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>662940</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>309880</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>680720</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>248920</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3280410" cy="2049780"/>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>398145</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1621790</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPr id="4" name="图片 3" descr="香港-原图(1)"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2232660" y="627380"/>
-          <a:ext cx="3280410" cy="2049780"/>
+        <a:xfrm rot="20880000">
+          <a:off x="1309370" y="883920"/>
+          <a:ext cx="2961640" cy="1372870"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -837,7 +837,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1127,15 +1127,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="13.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="21.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.8888888888889" customWidth="1"/>
-    <col min="5" max="5" width="10.4444444444444" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" customWidth="1"/>
-    <col min="7" max="7" width="12.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="13.8909090909091" customWidth="1"/>
+    <col min="3" max="3" width="21.6636363636364" customWidth="1"/>
+    <col min="4" max="4" width="10.8909090909091" customWidth="1"/>
+    <col min="5" max="5" width="10.4454545454545" customWidth="1"/>
+    <col min="6" max="6" width="9.33636363636364" customWidth="1"/>
+    <col min="7" max="7" width="12.5545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:7">
